--- a/config/held_item/items.xlsx
+++ b/config/held_item/items.xlsx
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>!!!廃棄1</t>
+          <t>! ! !废弃1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>!!!廃棄2</t>
+          <t>! ! !废弃2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>氷晶のオーブ</t>
+          <t>冰晶球体</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AG8" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>彩色インク</t>
+          <t>彩色墨水</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="AG9" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>七色の羽</t>
+          <t>七色羽毛</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>星霊の核</t>
+          <t>星灵的核心</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AG12" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>旅の日記</t>
+          <t>旅行日记</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="AG13" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>深青の葉</t>
+          <t>深蓝色的叶子</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="AG14" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>キャンディ</t>
+          <t>糖果</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AG15" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>時空バンド</t>
+          <t>时空波段</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AG16" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>光翼の布</t>
+          <t>光翅膀布</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="AG17" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>青いリボン</t>
+          <t>蓝色丝带</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AG18" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>混元の石</t>
+          <t>混元的石头</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AG19" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ヒマワリ</t>
+          <t>向日葵</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AG20" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>栄誉の帯</t>
+          <t>荣誉腰带</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AG21" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>花ブローチ</t>
+          <t>鲜花胸针</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="AG22" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>研究眼鏡</t>
+          <t>研究眼镜</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="AG23" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>占導のオーブ</t>
+          <t>占卜的球体</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="AG24" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>先制の爪</t>
+          <t>领先的爪子</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="AG25" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>虫メガネ</t>
+          <t>放大镜</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AG26" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>果物缶詰</t>
+          <t>水果罐头</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AG27" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>制御盤</t>
+          <t>控制面板</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="AG28" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>増幅器</t>
+          <t>放大器</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AG29" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>王者の証</t>
+          <t>王者的证明</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AG30" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ハーブ</t>
+          <t>药草</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AG31" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>てるてる坊主</t>
+          <t>晴天娃娃</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AG32" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>海の砂</t>
+          <t>大海的沙子</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="AG33" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>スカーフ</t>
+          <t>围巾</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="AG34" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>呪いの札</t>
+          <t>诅咒牌</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="AG35" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>竜の牙</t>
+          <t>龙牙</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="AG36" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>鉄鉱石</t>
+          <t>铁矿石</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="AG37" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>黒帯</t>
+          <t>黑带</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="AG38" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>防護フィルム</t>
+          <t>防护膜</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="AG39" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>改造チップ</t>
+          <t>改造芯片</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="AG40" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AG41" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>奇妙な香水</t>
+          <t>奇怪的香水</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="AG42" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>ハートの雫</t>
+          <t>心形水滴</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="AG43" s="1" t="inlineStr">
         <is>
-          <t>装飾ガチャで獲得できる</t>
+          <t>可以通过装饰卡获得</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>対戦通信機</t>
+          <t>对战通信机</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>リアルタイム対戦商店で獲得できる</t>
+          <t>可以在实时对战商店获得</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>時空マスク</t>
+          <t>时空面具</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>永劫の剣</t>
+          <t>永恒之剑</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>赤焔の爪</t>
+          <t>红色火焰爪</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>不朽の盾</t>
+          <t>不朽之盾</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>コアバンド</t>
+          <t>核心带</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>アームギア</t>
+          <t>臂齿轮</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>精霊の笛</t>
+          <t>精灵之笛</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>共鳴元素</t>
+          <t>共振元素</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>ブルーギア</t>
+          <t>蓝色齿轮</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>シルスコープ</t>
+          <t>希尔斯普</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>宝石の腕輪</t>
+          <t>宝石手镯</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>サイバー眼鏡</t>
+          <t>网络眼镜</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>ヘッドギア</t>
+          <t>头套</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>超音デバイス</t>
+          <t>超声波设备</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>音波ディスク</t>
+          <t>声波光盘</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>真実の鏡</t>
+          <t>真理之镜</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>神秘の首飾り</t>
+          <t>神秘项链</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>銀装シールド</t>
+          <t>银色护盾</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>武士仮面</t>
+          <t>武士假面</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>邪鬼仮面</t>
+          <t>魔鬼假面</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>シディアの花</t>
+          <t>西迪亚花</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>ソール時砂</t>
+          <t>索尔砂</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>遺因スパイク</t>
+          <t>遗因扣球</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>神の王冠</t>
+          <t>上帝的王冠</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
